--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/MONTANA_2021.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2021/MONTANA_2021.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Casas Grandes</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -597,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C17">
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Saucillo</t>
@@ -675,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Valle de Zaragoza</t>
+          <t>Valle De Zaragoza</t>
         </is>
       </c>
       <c r="C23">
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Comala</t>
@@ -732,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -747,7 +847,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -776,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -789,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -802,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -815,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -846,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -859,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Total</t>
@@ -874,7 +1009,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -916,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -929,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -942,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Tonatico</t>
@@ -955,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Total</t>
@@ -986,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Doctor Mora</t>
@@ -999,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1012,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>León</t>
@@ -1025,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1038,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Villagrán</t>
@@ -1051,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1071,7 +1266,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C51">
@@ -1082,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C52">
@@ -1095,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C53">
@@ -1108,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C54">
@@ -1121,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C55">
@@ -1134,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C56">
@@ -1147,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -1160,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -1173,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C59">
@@ -1186,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C60">
@@ -1199,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1230,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C63">
@@ -1243,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C64">
@@ -1256,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1287,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C67">
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -1313,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>El Grullo</t>
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1339,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -1352,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -1365,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C73">
@@ -1378,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Sayula</t>
@@ -1391,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -1404,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C76">
@@ -1417,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C77">
@@ -1430,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -1443,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1474,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1487,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1518,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1531,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1562,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MonteMorelos</t>
+          <t>Montemorelos</t>
         </is>
       </c>
       <c r="C87">
@@ -1575,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -1588,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1608,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C90">
@@ -1619,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -1632,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -1645,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>San Lucas Zoquiápam</t>
@@ -1658,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1689,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Cuyoaco</t>
@@ -1702,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -1715,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1728,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1759,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1772,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1803,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -1816,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -1829,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Santo Domingo</t>
@@ -1842,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1873,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Salvador Alvarado</t>
@@ -1886,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1917,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Nogales</t>
@@ -1930,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Ures</t>
@@ -1943,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1974,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2005,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -2018,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2049,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Amatlán de los Reyes</t>
+          <t>Amatlán De Los Reyes</t>
         </is>
       </c>
       <c r="C121">
@@ -2062,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Calcahualco</t>
@@ -2075,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -2088,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Coscomatepec</t>
@@ -2101,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -2114,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2145,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Juan Aldama</t>
@@ -2158,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C129">
@@ -2171,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -2184,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2207,41 +2727,6 @@
       </c>
       <c r="D132">
         <v>1</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 701,861</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Mayo de 2022</t>
-        </is>
       </c>
     </row>
   </sheetData>
